--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.708026279363244</v>
+        <v>0.7650542703965272</v>
       </c>
       <c r="D2" t="n">
-        <v>5.75</v>
+        <v>0.9343750000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>12.3942603118394</v>
+        <v>2.014067300673902</v>
       </c>
       <c r="F2" t="n">
-        <v>12.16202683176107</v>
+        <v>1.976329360161174</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.563033903950618</v>
+        <v>1.066493009391976</v>
       </c>
       <c r="D3" t="n">
-        <v>5.755254371863815</v>
+        <v>0.9352288354278699</v>
       </c>
       <c r="E3" t="n">
-        <v>12.3942603118394</v>
+        <v>2.014067300673902</v>
       </c>
       <c r="F3" t="n">
-        <v>12.16202683176107</v>
+        <v>1.976329360161174</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.49849001689684</v>
+        <v>2.681004627745736</v>
       </c>
       <c r="D4" t="n">
-        <v>16.99053009262642</v>
+        <v>2.760961140051793</v>
       </c>
       <c r="E4" t="n">
-        <v>12.3942603118394</v>
+        <v>2.014067300673902</v>
       </c>
       <c r="F4" t="n">
-        <v>12.16202683176107</v>
+        <v>1.976329360161174</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.19611988926567</v>
+        <v>3.606869482005672</v>
       </c>
       <c r="D5" t="n">
-        <v>22.75474316163398</v>
+        <v>3.697645763765522</v>
       </c>
       <c r="E5" t="n">
-        <v>12.3942603118394</v>
+        <v>2.014067300673902</v>
       </c>
       <c r="F5" t="n">
-        <v>12.16202683176107</v>
+        <v>1.976329360161174</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.93617946532201</v>
+        <v>8.439629163114827</v>
       </c>
       <c r="D6" t="n">
-        <v>51.51351423636703</v>
+        <v>8.370946063409642</v>
       </c>
       <c r="E6" t="n">
-        <v>12.3942603118394</v>
+        <v>2.014067300673902</v>
       </c>
       <c r="F6" t="n">
-        <v>12.16202683176107</v>
+        <v>1.976329360161174</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.63703843802945</v>
+        <v>2.378518746179787</v>
       </c>
       <c r="D7" t="n">
-        <v>13.81027724632484</v>
+        <v>2.244170052527786</v>
       </c>
       <c r="E7" t="n">
-        <v>12.3942603118394</v>
+        <v>2.014067300673902</v>
       </c>
       <c r="F7" t="n">
-        <v>12.16202683176107</v>
+        <v>1.976329360161174</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.35225205431786</v>
+        <v>4.282240958826652</v>
       </c>
       <c r="D8" t="n">
-        <v>25.65362590442439</v>
+        <v>4.168714209468964</v>
       </c>
       <c r="E8" t="n">
-        <v>12.3942603118394</v>
+        <v>2.014067300673902</v>
       </c>
       <c r="F8" t="n">
-        <v>12.16202683176107</v>
+        <v>1.976329360161174</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.18956057104097</v>
+        <v>3.118303592794158</v>
       </c>
       <c r="D9" t="n">
-        <v>19.92835959454263</v>
+        <v>3.238358434113178</v>
       </c>
       <c r="E9" t="n">
-        <v>12.3942603118394</v>
+        <v>2.014067300673902</v>
       </c>
       <c r="F9" t="n">
-        <v>12.16202683176107</v>
+        <v>1.976329360161174</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.8662785529743</v>
+        <v>1.928270264858324</v>
       </c>
       <c r="D10" t="n">
-        <v>25.8261806777045</v>
+        <v>4.196754360126981</v>
       </c>
       <c r="E10" t="n">
-        <v>12.3942603118394</v>
+        <v>2.014067300673902</v>
       </c>
       <c r="F10" t="n">
-        <v>12.16202683176107</v>
+        <v>1.976329360161174</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.80675881712094</v>
+        <v>4.031098307782154</v>
       </c>
       <c r="D11" t="n">
-        <v>27.03635453640457</v>
+        <v>4.393407612165742</v>
       </c>
       <c r="E11" t="n">
-        <v>12.3942603118394</v>
+        <v>2.014067300673902</v>
       </c>
       <c r="F11" t="n">
-        <v>12.16202683176107</v>
+        <v>1.976329360161174</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>10.5228052812965</v>
+        <v>1.709955858210682</v>
       </c>
       <c r="D12" t="n">
-        <v>30.89221401480769</v>
+        <v>5.01998477740625</v>
       </c>
       <c r="E12" t="n">
-        <v>12.3942603118394</v>
+        <v>2.014067300673902</v>
       </c>
       <c r="F12" t="n">
-        <v>12.16202683176107</v>
+        <v>1.976329360161174</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
